--- a/artfynd/A 6906-2025 artfynd.xlsx
+++ b/artfynd/A 6906-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111629742</v>
+        <v>118075132</v>
       </c>
       <c r="B4" t="n">
-        <v>103438</v>
+        <v>102862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,20 +971,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1885</v>
+        <v>837</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klockgentiana</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gentiana pneumonanthe</t>
+          <t>Hypericum pulchrum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -992,22 +992,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Iglasjön, VNV om, Hl</t>
+          <t>100 m V Iglasjön, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332168</v>
+        <v>332287</v>
       </c>
       <c r="R4" t="n">
-        <v>6363407</v>
+        <v>6363270</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,28 +1043,18 @@
           <t>Ölmevalla</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>N-Kun-0023</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lokalen kraftigt igenväxt med pors</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
@@ -1059,6 +1063,16 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Hedtallskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant i tallskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1070,268 +1084,7 @@
           <t>Harald Nordius</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>118075132</v>
-      </c>
-      <c r="B5" t="n">
-        <v>102862</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>837</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Hedjohannesört</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hypericum pulchrum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>100 m V Iglasjön, Hl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>332287</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6363270</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kungsbacka</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Ölmevalla</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Hedtallskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Vägkant i tallskog</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Harald Nordius</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Harald Nordius</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>119970430</v>
-      </c>
-      <c r="B6" t="n">
-        <v>102952</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>837</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Hedjohannesört</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Hypericum pulchrum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Furåsen, 100 m SV Iglasjön, Hl</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>332288</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6363270</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Kungsbacka</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ölmevalla</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>N-Kun-0482</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Lars-Erik Magnusson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Harald Nordius</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6906-2025 artfynd.xlsx
+++ b/artfynd/A 6906-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110583148</v>
+        <v>108715976</v>
       </c>
       <c r="B3" t="n">
-        <v>101243</v>
+        <v>96688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,54 +827,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>837</v>
+        <v>6052779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypericum pulchrum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>100 m V Iglasjön, Hl</t>
+          <t>Väst om Iglasjön, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332288.0131189647</v>
+        <v>332336</v>
       </c>
       <c r="R3" t="n">
-        <v>6363270.462253833</v>
+        <v>6363392</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,27 +889,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mest knopp men en utslagen blomma</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,7 +914,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägkant i tallskog</t>
+          <t>Tallskog med lingonris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118075132</v>
+        <v>110583148</v>
       </c>
       <c r="B4" t="n">
-        <v>102862</v>
+        <v>101243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -994,7 +967,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1004,7 +977,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1015,10 +988,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332287</v>
+        <v>332288.0131189647</v>
       </c>
       <c r="R4" t="n">
-        <v>6363270</v>
+        <v>6363270.462253833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1045,12 +1018,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mest knopp men en utslagen blomma</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1085,6 +1073,135 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118075132</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102862</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>837</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hedjohannesört</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hypericum pulchrum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>100 m V Iglasjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>332287</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6363270</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ölmevalla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Hedtallskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant i tallskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Harald Nordius</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Harald Nordius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
